--- a/260823.xlsx
+++ b/260823.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92ECB1F7-292B-475F-A6CE-9CD1481EEBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF0C8F7-9EE3-4F17-BA09-793F1A1EE6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7020" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="4110" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,20 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>durchleuchten und beleuchten wollen.
-Denn eines muss klar sein: in Deutschland Morde begangen hat.
-Und eine Folge war die Übernahme dieses Verfahrens Freital.
-Geuther: Und gerade da hatte die Aufdeckung der NSU-Taten ja auch tatsächlich Konsequenzen für Ihre Behörde bei der Frage der Übernahme und der Zuständigkeit.
-Dafür muss es ja immer einen besonderen Grund geben, sonst sind die Landesbehörden zuständig.
-Und in der Vergangenheit gab es da auch schon Streit.
-wenn es Anhaltspunkte gibt zum Beispiel, ob ein Fall besondere Bedeutung hat.
-Klappt das denn jetzt?
-Frank: Wir stehen in einem sehr engen Austausch.
-Wir haben in den letzten anderthalb Jahren</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Scholz: Wir sind uns alle einig:
 Und Anfang des nächsten Jahres wird der Parteivorsitzende dazu einen Vorschlag machen.
@@ -70,6 +57,15 @@
 Und letztlich macht es aber auch die Arbeit leichter, weil wir,  heute über Computerisierung, über Roboter und Ähnliches ganz anders gestaltet haben, und die körperliche Beanspruchung der Mitarbeiterinnen und Mitarbeiter ist deutlich geringer.
 Hahne: Im Business Barometer der deutsch-amerikanischen Handelskammer </t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Morde begangen</t>
+  </si>
+  <si>
+    <t>Anhaltspunkte</t>
+  </si>
+  <si>
+    <t>letzten anderthalb</t>
   </si>
 </sst>
 </file>
@@ -397,15 +393,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F7565E-170B-48C9-B028-8806F747DCD7}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="406" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -424,7 +430,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="308" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -443,7 +449,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="308" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -462,7 +468,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="252" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/260823.xlsx
+++ b/260823.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF0C8F7-9EE3-4F17-BA09-793F1A1EE6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FD7ABC-3702-4CB4-B454-ACCC665FD531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="4110" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10500" yWindow="4110" windowWidth="15010" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,28 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Scholz: Wir sind uns alle einig:
-Und Anfang des nächsten Jahres wird der Parteivorsitzende dazu einen Vorschlag machen.
-sonst wäre er übrigens auch ein schlechter Parteivorsitzender.
-Detjen: Und Sie gehören selbst zu den Mehreren, auf die Sigmar Gabriel auch immer wieder gezeigt hat, die in der SPD noch mögliche Kanzlerkanditen wären.
-Scholz: allgemein mehreren Männern und Frauen in der Führung der deutschen Sozialdemokratie zutraut.
-Trotzdem gilt, auf globale Themen, mit denen man sich gegenwärtig nicht vorstellen kann, wie da eine gemeinsame Regierung funktionieren sollte.
-dass die in der nächsten Zeit noch die Wende schaffen, dass sie regierungsgeeignet in einem deutschen Staat sind.
-Ich halte das nicht für möglich.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dass es das alles nicht zum Nulltarif gibt.
-Also, woher kommt das Geld?
-Gabriel: wo es uns wirtschaftlich gut geht und wir Überschüsse produzieren.
-Wir wären nicht klug beraten.
-In Europa ist es heute so, dass jeder Bäckermeister in Deutschland höhere Steuersätze zahlt als große Konzerne wie Amazon, Google und manche anderen, Starbucks, gigantische Gewinne zum Beispiel in Deutschland gemacht werden, aber nur ein Prozent Steuern gezahlt werden.
-Ich glaube nun auch nicht, dass wir das alles kriegen werden, aber stellen Sie sich vor, wir würden es schaffen, wenigstens zehn Prozent davon zu bekommen, indem wir in Europa diese Briefkastenfirmen bekämpfen, dass wir eine gemeinsame Grundlage der Besteuerung haben.
-Ich will ja gar nicht gleiche Steuersätze - das ist eine Illusion, das wird man nicht hinkriegen -, aber sagen wir mal, in Europa etwas zu erkennen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">Mattes: Nun, es kommen natürlich andere Voraussetzungen auf die Mitarbeiter zu.
 Neben der manuellen Tätigkeit ist die Bedienung von Computern, eine Aufgabe, die fast gang und gäbe geworden ist.
@@ -66,6 +44,21 @@
   </si>
   <si>
     <t>letzten anderthalb</t>
+  </si>
+  <si>
+    <t>alle einig</t>
+  </si>
+  <si>
+    <t>vorstellen kann, wie da</t>
+  </si>
+  <si>
+    <t>Überschüsse</t>
+  </si>
+  <si>
+    <t>stellen Sie sich vor, wir würden es schaffen, wenigstens</t>
+  </si>
+  <si>
+    <t>Illusion, das wird man nicht hinkriegen -, aber sagen wir mal</t>
   </si>
 </sst>
 </file>
@@ -393,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F7565E-170B-48C9-B028-8806F747DCD7}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
@@ -401,16 +394,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -421,35 +424,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0BA94E-C2F9-4B3B-9E53-3881244C59BB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="33.58203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="308" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0424BA2-CCCE-4D28-996D-8C905E3534E7}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="308" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -458,7 +452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C469824-1C76-49CB-B91D-D4076DD3FBB6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -468,7 +462,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="252" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
